--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/SOUTH_CAROLINA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/SOUTH_CAROLINA_2023.xlsx
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C161">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C260">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C375">
